--- a/用卷/1985.xlsx
+++ b/用卷/1985.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82BE90A-F550-4F8D-964B-2C3975345955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22819595-6FEC-41C9-AFD8-603AD57D5C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="55">
   <si>
     <t>年份</t>
   </si>
@@ -184,10 +184,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>辽宁其他类</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1985年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地)</t>
   </si>
   <si>
@@ -208,6 +204,14 @@
   </si>
   <si>
     <t>广西</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>辽宁</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -678,7 +682,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -775,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>42</v>
@@ -879,119 +883,119 @@
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>1985</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
+      <c r="A18" s="11">
+        <v>1985</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="9"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1985</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>1985</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
-        <v>1985</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>51</v>
-      </c>
       <c r="C20" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="18"/>
+        <v>42</v>
+      </c>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
+      <c r="A21" s="11">
         <v>1985</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>1985</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1985</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>12</v>
+      <c r="B23" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1985</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="13"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>1985</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="9"/>
+      <c r="D25" s="13"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1985</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>1985</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>42</v>
@@ -1002,139 +1006,139 @@
       <c r="A28" s="1">
         <v>1985</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>36</v>
+      <c r="B28" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="9"/>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>1985</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>17</v>
+      <c r="B29" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>1985</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1985</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="11"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
-        <v>1985</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="11"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>1985</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="C32" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="9"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="7"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="4">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>45</v>
+        <v>20</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" s="4">
         <v>3</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="19"/>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="4">
         <v>2</v>
@@ -1142,11 +1146,11 @@
       <c r="C40" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="7"/>
+      <c r="D40" s="19"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" s="4">
         <v>2</v>
@@ -1158,7 +1162,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="4">
         <v>2</v>
@@ -1170,7 +1174,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="4">
         <v>2</v>
@@ -1180,9 +1184,21 @@
       </c>
       <c r="D43" s="7"/>
     </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
